--- a/site/exports/seu-materials-metal.xlsx
+++ b/site/exports/seu-materials-metal.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院／金属材料系</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>现职、校区与全部教育年月未核；2024-08-23页面发布时间与2026年作品不等人事更新。；东南大学本科只学习层次；中科院金属所硕士原具体资格称谓保留，授位日期与法律主体未知。；中科院金属所—维也纳大学联合培养博士为单一培养事件；主培、访问及授位主体和实际博士获授未单独核实，不造两学位。；原日本丰桥技科大学JSPS与美国Drexel研究仅泛述，未认定博士后或新学位；本人教授、博士生导师及首席教授来源标签不生成其自身导师。；仅原两条代表性论文；已留存出版者元数据，不含全文、附属数据或补充材料。教学原文未结构化收录，空课程不代表无授课。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18.2" customWidth="1" min="4" max="4"/>
+    <col width="19.6" customWidth="1" min="2" max="2"/>
+    <col width="16.8" customWidth="1" min="3" max="3"/>
+    <col width="23.8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -600,7 +654,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="65" customWidth="1" min="17" max="17"/>
@@ -1000,14 +1054,469 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>原文仅东南大学本科；不把本科标签推为学士学位或授位。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院金属研究所</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>具名个人简介列“中科院金属所硕士”，按本人具体资格记来源报告已获硕士；原培养机构名保留，法律授位主体及授位年/月/日未知，未核学位证。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>joint_training</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>原文中科院金属所-维也纳大学联合培养博士。仅记录联合培养非授位事件；博士学位是否实际获授及授位院校均未知，不制造两枚博士学位，也不猜主培/访学单位。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>postdoc</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>维也纳大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>原文明注博士后，为非学位研究经历。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>主任研究员兼国际部长助理</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>日本产业技术综合研究所（AIST）</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>回国前任职；未披露年月。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>学术委员会主任</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>东南大学材料学院</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>简介记历任首届学术委员会主任并自述现任；无可验证2026现职日期，导航关闭。 原记首届及现任主任，具体年月未知。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>院长</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>东南大学材料学院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>简介明确历任，起止未知。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>党委书记</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>东南大学材料学院</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>简介明确历任，起止未知。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1110,19 +1619,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30.8" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
     <col width="64.39999999999999" customWidth="1" min="9" max="9"/>
-    <col width="57.4" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1245,11 +1754,135 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Atomically Tailored Fe-Dy Dual-Atom Sites With 3d-4f Orbital Coupling for Enhanced Bifunctional Oxygen Electrocatalysis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>10.1002/adma.202520359</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/adma.202520359</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Official named profile representative work list matched against publisher title/authors; publisher explicitly lists ZhengMing Sun, School of Materials Science and Engineering, Southeast University.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>publisher_metadata_body_read</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>原作者：Jingyuan Qiao、Yurong You、Weihang Feng、Lingqiao Kong、Ye Chen、Wei He、ZhengMing Sun。Advanced Materials 2026年，卷38，期17，文章号e20359；在线发表日2026-02-22，不同于卷期年。已留存出版者元数据核题名、作者与本人东南材料学院署名；非全文阅读，DOI后缀不当出版年。</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Microphase-Separated Hydrogel Electrolytes with Selective Ion Transportation Pathways for Flexible Zinc-Ion Batteries</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10.1002/adma.202518881</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/adma.202518881</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Official named profile representative work list matched against publisher title/authors; publisher explicitly lists ZhengMing Sun, School of Materials Science and Engineering, Southeast University.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>publisher_metadata_body_read</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>原作者：Huan Xia、Tao Shui、Xiaotian Wan、Yixi Chen、Fengyi Wang、Chunyang Miao、Xin Cao、Bingyige Pan、Zihe Pan、Qian Xie、Ye Chen、Wei Zhang、ZhengMing Sun。Advanced Materials 2026年，卷38，期8，文章号e18881；在线发表日2025-11-29，不同于卷期年。已留存出版者元数据核题名、作者与本人东南材料学院署名；非全文阅读，DOI后缀不当出版年。</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1261,7 +1894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1458,13 +2091,203 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>seu-materials-roster</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/szry/list.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>official_directory_body_read</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>seu-materials-structure</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/xsjg/list.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>official_structure_body_read</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>seu-sunzhengming-profile</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://smse.seu.edu.cn/2018/1007/c2590a242137/page.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>official_individual_profile_body_read</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>seu-sun-work1-publisher</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/abs/10.1002/adma.202520359?af=R</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>publisher_metadata_body_read</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>孙正明</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>seu-sun-work2-publisher</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://advanced.onlinelibrary.wiley.com/doi/10.1002/adma.202518881</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>publisher_metadata_body_read</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>seu</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>东南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
